--- a/V3.0/Bill Of Materials CartToolV3 routed.csv.xlsx
+++ b/V3.0/Bill Of Materials CartToolV3 routed.csv.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="105">
   <si>
     <t xml:space="preserve">﻿Category</t>
   </si>
@@ -112,7 +112,7 @@
     <t xml:space="preserve">48</t>
   </si>
   <si>
-    <t xml:space="preserve">R6,R7,R8,R9,R10,R11,R12,R13,R14,R15,R16,R17,R18,R19,R20,R21,R22,R23,R24,R25,R26,R27,R28,R29,R30,R31,R32,R33,R34,R35,R36,R37,R38,R39,R40,R41,R42,R43,R44,R45,R46,R47,R48,R49,R50,R51,R52,R53</t>
+    <t xml:space="preserve">R4,R8,R9,R10,R11,R12,R13,R14,R15,R22,R23,R24,R25,R26,R27,R28,R29,R30,R31,R32,R33,R34,R35,R36,R37,R38,R39,R40,R41,R42,R43,R44,R45,R46,R47,R48,R49,R50,R51,R52,R53,R55,R56,R57,R58,R59,R60,R61</t>
   </si>
   <si>
     <t xml:space="preserve">CR0805-JW-103ELF</t>
@@ -190,6 +190,21 @@
     <t xml:space="preserve">SOIC127P600X175-14N-CAP</t>
   </si>
   <si>
+    <t xml:space="preserve">U7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULN2803CDWR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.mouser.sg/ProductDetail/Texas-Instruments/ULN2803CDWR?qs=vvQtp7zwQdMA2JP56CSJyQ%3D%3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bipolar (BJT) Transistor Array 8 NPN Darlington 50V 500mA Surface Mount 20-SOIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOIC127P1030X265-20N</t>
+  </si>
+  <si>
     <t xml:space="preserve">U13</t>
   </si>
   <si>
@@ -226,7 +241,7 @@
     <t xml:space="preserve">24</t>
   </si>
   <si>
-    <t xml:space="preserve">Q1,Q2,Q3,Q4,Q5,Q6,Q7,Q8,Q9,Q10,Q11,Q12,Q13,Q14,Q15,Q16,Q17,Q18,Q19,Q20,Q21,Q22,Q23,Q24</t>
+    <t xml:space="preserve">Q2,Q3,Q4,Q5,Q9,Q10,Q11,Q12,Q13,Q14,Q15,Q16,Q17,Q18,Q19,Q20,Q21,Q22,Q23,Q24,Q25,Q26,Q27,Q28</t>
   </si>
   <si>
     <t xml:space="preserve">BSS138</t>
@@ -608,11 +623,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H1048576"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="174.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="175.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="143"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="255.71"/>
@@ -620,7 +635,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.42"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
@@ -646,7 +661,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
         <v>8</v>
       </c>
@@ -672,7 +687,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>8</v>
       </c>
@@ -698,7 +713,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>22</v>
       </c>
@@ -724,7 +739,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>22</v>
       </c>
@@ -750,7 +765,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>22</v>
       </c>
@@ -776,7 +791,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>40</v>
       </c>
@@ -802,7 +817,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>40</v>
       </c>
@@ -828,7 +843,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>40</v>
       </c>
@@ -854,7 +869,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>40</v>
       </c>
@@ -880,7 +895,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>40</v>
       </c>
@@ -906,87 +921,87 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="D12" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="F12" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="G12" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="H12" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="B13" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="H12" s="0" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="C13" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="D13" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F13" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" s="0" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="C14" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="0" t="s">
+      <c r="D14" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="G14" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="G14" s="0" t="s">
+      <c r="H14" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
         <v>84</v>
-      </c>
-      <c r="H14" s="0" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>79</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>16</v>
@@ -1007,63 +1022,87 @@
         <v>89</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="G16" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="H16" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="H16" s="0" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" s="0" t="s">
+      <c r="B18" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F17" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="H17" s="0" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="F18" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="https://www.mouser.sg/ProductDetail/Panasonic/EEU-FR1E471YB?qs=n1SRcuzDZT1JwIghP%252BP6vA%3D%3D"/>
@@ -1074,14 +1113,15 @@
     <hyperlink ref="E7" r:id="rId6" display="https://www.mouser.sg/ProductDetail/Texas-Instruments/SN74LS374DWR?qs=SL3LIuy2dWx46uWPzrGxvw%3D%3D"/>
     <hyperlink ref="E8" r:id="rId7" display="https://www.mouser.sg/ProductDetail/Texas-Instruments/SN74LS273NSR?qs=SL3LIuy2dWxsq%2FCTeVMKZg%3D%3D"/>
     <hyperlink ref="E9" r:id="rId8" display="https://www.mouser.sg/ProductDetail/Texas-Instruments/SN74LS04DR?qs=SL3LIuy2dWzOhepjTMFpMg%3D%3D"/>
-    <hyperlink ref="E10" r:id="rId9" display="https://www.mouser.sg/ProductDetail/E-Switch/TL59F260Q?qs=QtyuwXswaQiASDh1C66FNg%3D%3D"/>
-    <hyperlink ref="E11" r:id="rId10" display="https://www.mouser.sg/ProductDetail/Analog-Devices/ADM709LARZ?qs=BpaRKvA4VqHy5OxrBQwb0w%3D%3D"/>
-    <hyperlink ref="E12" r:id="rId11" display="https://www.mouser.sg/ProductDetail/onsemi-Fairchild/BSS138?qs=HK%252BeIG1iaahCeqBvjB4arg%3D%3D"/>
-    <hyperlink ref="E13" r:id="rId12" display="https://www.mouser.sg/ProductDetail/Cree-LED/C503C-RCN-CYCZaAA1?qs=mwfrHz%252BSIuGPYiPc7W1Mew%3D%3D"/>
-    <hyperlink ref="E14" r:id="rId13" display="https://www.mouser.com/ProductDetail/TE-Connectivity/5530843-4?qs=CWN9I2qbSLsRSJz%252BQBuIeg%3D%3D"/>
-    <hyperlink ref="E15" r:id="rId14" display="https://www.mouser.sg/ProductDetail/3M-Electronic-Solutions-Division/929975-01-20-RK?qs=4V84emjyG36rTUkvYfpt0A%3D%3D"/>
-    <hyperlink ref="E16" r:id="rId15" display="https://www.mouser.sg/ProductDetail/3M-Electronic-Solutions-Division/929850-01-02-10?qs=sGAEpiMZZMs%252BGHln7q6pm6DQXoV0bF8fKj%2FScW6NT6k%3D"/>
-    <hyperlink ref="E17" r:id="rId16" display="https://www.mouser.sg/ProductDetail/Samsung-Electro-Mechanics/CL05B104KO5NNNC?qs=hqM3L16%252BxlfT2SKOuAUq6Q%3D%3D"/>
+    <hyperlink ref="E10" r:id="rId9" display="https://www.mouser.sg/ProductDetail/Texas-Instruments/ULN2803CDWR?qs=vvQtp7zwQdMA2JP56CSJyQ%3D%3D"/>
+    <hyperlink ref="E11" r:id="rId10" display="https://www.mouser.sg/ProductDetail/E-Switch/TL59F260Q?qs=QtyuwXswaQiASDh1C66FNg%3D%3D"/>
+    <hyperlink ref="E12" r:id="rId11" display="https://www.mouser.sg/ProductDetail/Analog-Devices/ADM709LARZ?qs=BpaRKvA4VqHy5OxrBQwb0w%3D%3D"/>
+    <hyperlink ref="E13" r:id="rId12" display="https://www.mouser.sg/ProductDetail/onsemi-Fairchild/BSS138?qs=HK%252BeIG1iaahCeqBvjB4arg%3D%3D"/>
+    <hyperlink ref="E14" r:id="rId13" display="https://www.mouser.sg/ProductDetail/Cree-LED/C503C-RCN-CYCZaAA1?qs=mwfrHz%252BSIuGPYiPc7W1Mew%3D%3D"/>
+    <hyperlink ref="E15" r:id="rId14" display="https://www.mouser.com/ProductDetail/TE-Connectivity/5530843-4?qs=CWN9I2qbSLsRSJz%252BQBuIeg%3D%3D"/>
+    <hyperlink ref="E16" r:id="rId15" display="https://www.mouser.sg/ProductDetail/3M-Electronic-Solutions-Division/929975-01-20-RK?qs=4V84emjyG36rTUkvYfpt0A%3D%3D"/>
+    <hyperlink ref="E17" r:id="rId16" display="https://www.mouser.sg/ProductDetail/3M-Electronic-Solutions-Division/929850-01-02-10?qs=sGAEpiMZZMs%252BGHln7q6pm6DQXoV0bF8fKj%2FScW6NT6k%3D"/>
+    <hyperlink ref="E18" r:id="rId17" display="https://www.mouser.sg/ProductDetail/Samsung-Electro-Mechanics/CL05B104KO5NNNC?qs=hqM3L16%252BxlfT2SKOuAUq6Q%3D%3D"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
